--- a/ig/DM-FEVRIER-2026/ValueSet-JDV-J98-StatutHospitalier-RASS.xlsx
+++ b/ig/DM-FEVRIER-2026/ValueSet-JDV-J98-StatutHospitalier-RASS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="71">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20200424120000</t>
+    <t>20260223120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2020-04-24T12:00:00+01:00</t>
+    <t>2026-02-23T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -205,6 +205,12 @@
   </si>
   <si>
     <t>Clinicien hospitalier (R6152-701 et suivants du CSP)</t>
+  </si>
+  <si>
+    <t>SH19</t>
+  </si>
+  <si>
+    <t>Praticien hospitalier</t>
   </si>
   <si>
     <t>SH99</t>
@@ -481,7 +487,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -653,15 +659,23 @@
         <v>66</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>68</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
